--- a/Classifica_Campionato.xlsx
+++ b/Classifica_Campionato.xlsx
@@ -56,19 +56,19 @@
     <t>Pt. Totali</t>
   </si>
   <si>
+    <t>ReAlcolizzati</t>
+  </si>
+  <si>
+    <t>Black Gay United</t>
+  </si>
+  <si>
     <t>Canile Comunale Di Merate</t>
   </si>
   <si>
+    <t>FC Tumori</t>
+  </si>
+  <si>
     <t>Scroto FC</t>
-  </si>
-  <si>
-    <t>ReAlcolizzati</t>
-  </si>
-  <si>
-    <t>FC Tumori</t>
-  </si>
-  <si>
-    <t>Black Gay United</t>
   </si>
   <si>
     <t>CSKA LA RISSA</t>
@@ -269,31 +269,31 @@
         <v>4</v>
       </c>
       <c r="D5" s="6">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E5" s="6">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F5" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G5" s="6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H5" s="6">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I5" s="6">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J5" s="6">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="K5" s="7">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="L5" s="8">
-        <v>771</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="6">
@@ -307,31 +307,31 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E6" s="6">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F6" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G6" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H6" s="6">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="I6" s="6">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="J6" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K6" s="7">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="L6" s="8">
-        <v>772.5</v>
+        <v>2483.5</v>
       </c>
     </row>
     <row r="7">
@@ -345,31 +345,31 @@
         <v>4</v>
       </c>
       <c r="D7" s="6">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E7" s="6">
+        <v>13</v>
+      </c>
+      <c r="F7" s="6">
+        <v>12</v>
+      </c>
+      <c r="G7" s="6">
+        <v>10</v>
+      </c>
+      <c r="H7" s="6">
+        <v>56</v>
+      </c>
+      <c r="I7" s="6">
+        <v>51</v>
+      </c>
+      <c r="J7" s="6">
         <v>5</v>
       </c>
-      <c r="F7" s="6">
-        <v>2</v>
-      </c>
-      <c r="G7" s="6">
-        <v>4</v>
-      </c>
-      <c r="H7" s="6">
-        <v>27</v>
-      </c>
-      <c r="I7" s="6">
-        <v>15</v>
-      </c>
-      <c r="J7" s="6">
-        <v>12</v>
-      </c>
       <c r="K7" s="7">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="L7" s="8">
-        <v>807.5</v>
+        <v>2435.5</v>
       </c>
     </row>
     <row r="8">
@@ -383,31 +383,31 @@
         <v>4</v>
       </c>
       <c r="D8" s="6">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E8" s="6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F8" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G8" s="6">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H8" s="6">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I8" s="6">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J8" s="6">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="K8" s="7">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="L8" s="8">
-        <v>773.5</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="9">
@@ -421,31 +421,31 @@
         <v>4</v>
       </c>
       <c r="D9" s="6">
+        <v>35</v>
+      </c>
+      <c r="E9" s="6">
         <v>11</v>
       </c>
-      <c r="E9" s="6">
-        <v>4</v>
-      </c>
       <c r="F9" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G9" s="6">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H9" s="6">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="I9" s="6">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="J9" s="6">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="K9" s="7">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L9" s="8">
-        <v>743</v>
+        <v>2432.5</v>
       </c>
     </row>
     <row r="10">
@@ -459,31 +459,31 @@
         <v>4</v>
       </c>
       <c r="D10" s="6">
+        <v>35</v>
+      </c>
+      <c r="E10" s="6">
         <v>11</v>
       </c>
-      <c r="E10" s="6">
-        <v>4</v>
-      </c>
       <c r="F10" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G10" s="6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H10" s="6">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="I10" s="6">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J10" s="6">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="K10" s="7">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="L10" s="8">
-        <v>819</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="11">
@@ -497,31 +497,31 @@
         <v>4</v>
       </c>
       <c r="D11" s="6">
+        <v>35</v>
+      </c>
+      <c r="E11" s="6">
         <v>11</v>
       </c>
-      <c r="E11" s="6">
-        <v>4</v>
-      </c>
       <c r="F11" s="6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G11" s="6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H11" s="6">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="I11" s="6">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="J11" s="6">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="K11" s="7">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="L11" s="8">
-        <v>755</v>
+        <v>2406.5</v>
       </c>
     </row>
     <row r="12">
@@ -535,31 +535,31 @@
         <v>4</v>
       </c>
       <c r="D12" s="6">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E12" s="6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F12" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G12" s="6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H12" s="6">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="I12" s="6">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="J12" s="6">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="K12" s="7">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="L12" s="8">
-        <v>730</v>
+        <v>2395.5</v>
       </c>
     </row>
   </sheetData>
